--- a/EXCEL/Exercise Files/Chapter02/02_05_Forecast.xlsx
+++ b/EXCEL/Exercise Files/Chapter02/02_05_Forecast.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Curtis\Desktop\Exercise Files\Chapter02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8650F7F0-CDC7-4960-A1C4-CF5519D67E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89778C57-106F-43B0-969A-FEC13EE3EE04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trend" sheetId="1" r:id="rId1"/>
@@ -87,8 +87,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -141,12 +141,12 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -435,12 +435,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -448,7 +448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -456,7 +456,7 @@
         <v>345000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -464,7 +464,7 @@
         <v>285000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -472,7 +472,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -480,7 +480,7 @@
         <v>402000</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -488,7 +488,7 @@
         <v>199000</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -496,7 +496,7 @@
         <v>450000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -504,7 +504,7 @@
         <v>395000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -512,22 +512,22 @@
         <v>407000</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -540,15 +540,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.3828125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.15234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -562,7 +562,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -571,7 +571,7 @@
       </c>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -579,7 +579,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -587,7 +587,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -595,7 +595,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -603,7 +603,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -611,7 +611,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>10</v>
       </c>
@@ -619,7 +619,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>20</v>
       </c>
@@ -627,7 +627,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>20</v>
       </c>
@@ -635,7 +635,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>22</v>
       </c>
@@ -643,7 +643,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>45</v>
       </c>
@@ -651,7 +651,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>50</v>
       </c>
@@ -659,7 +659,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>50</v>
       </c>
@@ -667,7 +667,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>50</v>
       </c>
@@ -675,7 +675,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>75</v>
       </c>
@@ -683,7 +683,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>75</v>
       </c>
@@ -691,7 +691,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>75</v>
       </c>
@@ -699,7 +699,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>75</v>
       </c>
@@ -707,7 +707,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>85</v>
       </c>
@@ -715,7 +715,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>87</v>
       </c>
@@ -723,7 +723,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>99</v>
       </c>
@@ -731,7 +731,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>100</v>
       </c>
@@ -739,7 +739,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>125</v>
       </c>
@@ -747,7 +747,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>130</v>
       </c>
@@ -755,7 +755,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>145</v>
       </c>
@@ -763,7 +763,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>152</v>
       </c>
